--- a/processed_data/noise_imputed_data.xlsx
+++ b/processed_data/noise_imputed_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,17 +489,27 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>pollinators_mean_occupancy</t>
+          <t>plant_abundance_arable_unsmoothed_index</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>pollinating_wild_bees_mean_occupancy</t>
+          <t>plant_abundance_bog_and_heath_unsmoothed_index</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>pollinating_hoverflies_mean_occupancy</t>
+          <t>plant_abundance_grassland_unsmoothed_index</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>plant_abundance_woodland_unsmoothed_index</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>pollinators_mean_occupancy</t>
         </is>
       </c>
     </row>
@@ -526,14 +536,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>97.82443715520681</v>
-      </c>
-      <c r="P2" t="n">
-        <v>98.98556201417234</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>98.89247282897188</v>
       </c>
     </row>
     <row r="3">
@@ -545,13 +553,13 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>61.58531725838908</v>
+        <v>57.6805324621503</v>
       </c>
       <c r="G3" t="n">
-        <v>37.41456950749906</v>
+        <v>35.99182572955882</v>
       </c>
       <c r="H3" t="n">
-        <v>75.54996603647983</v>
+        <v>78.56375614204153</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -559,14 +567,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>101.922830424427</v>
-      </c>
-      <c r="P3" t="n">
-        <v>100.6343684244913</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>106.191992902992</v>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>102.6817117946486</v>
       </c>
     </row>
     <row r="4">
@@ -578,13 +584,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>108.2712811941221</v>
+        <v>107.9054889366746</v>
       </c>
       <c r="G4" t="n">
-        <v>70.4569883053364</v>
+        <v>71.53851143882322</v>
       </c>
       <c r="H4" t="n">
-        <v>127.2727353065887</v>
+        <v>131.908853146358</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -592,14 +598,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>103.5065268309099</v>
-      </c>
-      <c r="P4" t="n">
-        <v>101.2732435512358</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>107.2131425669783</v>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>104.5199114537688</v>
       </c>
     </row>
     <row r="5">
@@ -611,13 +615,13 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>95.96713509720961</v>
+        <v>96.32292948042024</v>
       </c>
       <c r="G5" t="n">
-        <v>64.58506795431674</v>
+        <v>65.11919420825747</v>
       </c>
       <c r="H5" t="n">
-        <v>122.5587366158348</v>
+        <v>121.0770169333258</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -625,14 +629,12 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>105.9760148064526</v>
-      </c>
-      <c r="P5" t="n">
-        <v>101.2376513452167</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>105.3477979104067</v>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>107.2460698354849</v>
       </c>
     </row>
     <row r="6">
@@ -644,13 +646,13 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>129.4592863250186</v>
+        <v>128.0761205114346</v>
       </c>
       <c r="G6" t="n">
-        <v>87.77305168422959</v>
+        <v>88.32398288274719</v>
       </c>
       <c r="H6" t="n">
-        <v>154.0276901335871</v>
+        <v>150.8638486085212</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -658,14 +660,12 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>107.6612128365975</v>
-      </c>
-      <c r="P6" t="n">
-        <v>101.8972349472553</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>106.5754681904492</v>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>107.2676535090134</v>
       </c>
     </row>
     <row r="7">
@@ -673,21 +673,21 @@
         <v>1985</v>
       </c>
       <c r="B7" t="n">
-        <v>99.59617671795709</v>
+        <v>100.664354282967</v>
       </c>
       <c r="C7" t="n">
-        <v>100.8368009057992</v>
+        <v>103.603990715092</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>94.41869754782802</v>
+        <v>91.43911788899035</v>
       </c>
       <c r="G7" t="n">
-        <v>74.76373427608121</v>
+        <v>76.35091075816145</v>
       </c>
       <c r="H7" t="n">
-        <v>101.834423462878</v>
+        <v>100.0488204785354</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -695,14 +695,12 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>109.2692756890843</v>
-      </c>
-      <c r="P7" t="n">
-        <v>100.88979985619</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>110.7252112319691</v>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>109.0525380523405</v>
       </c>
     </row>
     <row r="8">
@@ -710,21 +708,21 @@
         <v>1986</v>
       </c>
       <c r="B8" t="n">
-        <v>101.153274812784</v>
+        <v>99.12266085127129</v>
       </c>
       <c r="C8" t="n">
-        <v>98.46576725482676</v>
+        <v>96.67831397620299</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>86.61898467500018</v>
+        <v>88.07584869624637</v>
       </c>
       <c r="G8" t="n">
-        <v>66.6650792893282</v>
+        <v>67.78491736606793</v>
       </c>
       <c r="H8" t="n">
-        <v>95.73222662075909</v>
+        <v>96.68024284378387</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -732,14 +730,12 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>110.6692443433889</v>
-      </c>
-      <c r="P8" t="n">
-        <v>98.68523396789668</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>116.2916344181919</v>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>111.0507378130034</v>
       </c>
     </row>
     <row r="9">
@@ -747,21 +743,21 @@
         <v>1987</v>
       </c>
       <c r="B9" t="n">
-        <v>96.31064754848983</v>
+        <v>96.2093263078355</v>
       </c>
       <c r="C9" t="n">
-        <v>114.6115831486119</v>
+        <v>108.2899183943559</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>89.71324221931576</v>
+        <v>89.20656563757696</v>
       </c>
       <c r="G9" t="n">
-        <v>76.25410282416112</v>
+        <v>76.69344743019192</v>
       </c>
       <c r="H9" t="n">
-        <v>88.04828202746839</v>
+        <v>85.23714436643455</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -769,14 +765,12 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>113.9299466967755</v>
-      </c>
-      <c r="P9" t="n">
-        <v>97.70549488762607</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>117.3522057127418</v>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>111.4090632619278</v>
       </c>
     </row>
     <row r="10">
@@ -784,21 +778,21 @@
         <v>1988</v>
       </c>
       <c r="B10" t="n">
-        <v>88.75615419886374</v>
+        <v>88.68368620848982</v>
       </c>
       <c r="C10" t="n">
-        <v>106.8596011360144</v>
+        <v>113.8113365617189</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>75.18905135479605</v>
+        <v>76.87948034931576</v>
       </c>
       <c r="G10" t="n">
-        <v>59.34007052043038</v>
+        <v>57.37085338416112</v>
       </c>
       <c r="H10" t="n">
-        <v>80.69737105864891</v>
+        <v>85.14275288746839</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -806,14 +800,12 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>112.0796104135007</v>
-      </c>
-      <c r="P10" t="n">
-        <v>95.68443528132984</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>118.2810338386186</v>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>113.0840124967755</v>
       </c>
     </row>
     <row r="11">
@@ -821,21 +813,21 @@
         <v>1989</v>
       </c>
       <c r="B11" t="n">
-        <v>98.73621421378607</v>
+        <v>96.43756618154271</v>
       </c>
       <c r="C11" t="n">
-        <v>103.85683026389</v>
+        <v>100.6978584708057</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>102.5145850177723</v>
+        <v>99.10506862270385</v>
       </c>
       <c r="G11" t="n">
-        <v>68.6169926182571</v>
+        <v>68.34309624641494</v>
       </c>
       <c r="H11" t="n">
-        <v>124.2476536421346</v>
+        <v>121.4177880378158</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -843,14 +835,12 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>109.753856849969</v>
-      </c>
-      <c r="P11" t="n">
-        <v>94.51043880652422</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>117.386390494683</v>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>107.8154706770358</v>
       </c>
     </row>
     <row r="12">
@@ -858,52 +848,50 @@
         <v>1990</v>
       </c>
       <c r="B12" t="n">
-        <v>92.23825461617554</v>
+        <v>94.44815399439025</v>
       </c>
       <c r="C12" t="n">
-        <v>109.6868687653029</v>
+        <v>110.9054904721721</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1361798138708779</v>
+        <v>0.1309756364382969</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3376576049516618</v>
+        <v>0.3482443318188456</v>
       </c>
       <c r="F12" t="n">
-        <v>110.0106554641395</v>
+        <v>108.8533813750928</v>
       </c>
       <c r="G12" t="n">
-        <v>79.41220143433701</v>
+        <v>79.85471302778663</v>
       </c>
       <c r="H12" t="n">
-        <v>123.5017756142211</v>
+        <v>119.0633696937123</v>
       </c>
       <c r="I12" t="n">
-        <v>100.6441015037453</v>
+        <v>95.51642187822166</v>
       </c>
       <c r="J12" t="n">
-        <v>103.4416836541908</v>
+        <v>104.8390316134736</v>
       </c>
       <c r="K12" t="n">
-        <v>89.90567116296384</v>
+        <v>91.61165122218897</v>
       </c>
       <c r="L12" t="n">
-        <v>109.3087112300104</v>
+        <v>111.5981121599566</v>
       </c>
       <c r="M12" t="n">
-        <v>122.4244994163786</v>
+        <v>125.1020180025029</v>
       </c>
       <c r="N12" t="n">
-        <v>106.6695137026823</v>
-      </c>
-      <c r="O12" t="n">
-        <v>108.1862542963098</v>
-      </c>
-      <c r="P12" t="n">
-        <v>94.41116938408557</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>115.3885094882374</v>
+        <v>105.4532244505741</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>108.0624276653752</v>
       </c>
     </row>
     <row r="13">
@@ -911,52 +899,50 @@
         <v>1991</v>
       </c>
       <c r="B13" t="n">
-        <v>91.66554272451103</v>
+        <v>92.18039704886891</v>
       </c>
       <c r="C13" t="n">
-        <v>110.1938624382179</v>
+        <v>105.113983736779</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1302020672902887</v>
+        <v>0.1342103199364943</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4044829039648282</v>
+        <v>0.3808273129859217</v>
       </c>
       <c r="F13" t="n">
-        <v>103.6258290919238</v>
+        <v>100.6368408885792</v>
       </c>
       <c r="G13" t="n">
-        <v>62.23842040969186</v>
+        <v>64.05348438557068</v>
       </c>
       <c r="H13" t="n">
-        <v>133.9604676455967</v>
+        <v>134.1678598036058</v>
       </c>
       <c r="I13" t="n">
-        <v>93.35450541741683</v>
+        <v>93.83999890064639</v>
       </c>
       <c r="J13" t="n">
-        <v>73.82104857169836</v>
+        <v>76.33784999521967</v>
       </c>
       <c r="K13" t="n">
-        <v>114.310373789336</v>
+        <v>111.8186193845522</v>
       </c>
       <c r="L13" t="n">
-        <v>99.50902568096966</v>
+        <v>100.49333829731</v>
       </c>
       <c r="M13" t="n">
-        <v>102.985907849308</v>
+        <v>104.1046171358489</v>
       </c>
       <c r="N13" t="n">
-        <v>96.84548649228029</v>
-      </c>
-      <c r="O13" t="n">
-        <v>104.9450147860454</v>
-      </c>
-      <c r="P13" t="n">
-        <v>93.76309480219237</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>113.1849492983138</v>
+        <v>100.2121004616828</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>108.8243407214985</v>
       </c>
     </row>
     <row r="14">
@@ -964,52 +950,50 @@
         <v>1992</v>
       </c>
       <c r="B14" t="n">
-        <v>91.93361426902285</v>
+        <v>91.08894782296687</v>
       </c>
       <c r="C14" t="n">
-        <v>100.445255486965</v>
+        <v>101.5981363043626</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1277258273992943</v>
+        <v>0.1257264428699919</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4094326785196193</v>
+        <v>0.396783911085925</v>
       </c>
       <c r="F14" t="n">
-        <v>126.818322700341</v>
+        <v>128.1454674682528</v>
       </c>
       <c r="G14" t="n">
-        <v>88.32409758421026</v>
+        <v>88.54883778937911</v>
       </c>
       <c r="H14" t="n">
-        <v>154.0815038724894</v>
+        <v>154.5524640675222</v>
       </c>
       <c r="I14" t="n">
-        <v>108.2164409691122</v>
+        <v>111.3564883607736</v>
       </c>
       <c r="J14" t="n">
-        <v>103.5876421182182</v>
+        <v>102.9597695332031</v>
       </c>
       <c r="K14" t="n">
-        <v>116.9641518122232</v>
+        <v>118.4136452238326</v>
       </c>
       <c r="L14" t="n">
-        <v>119.3121997028265</v>
+        <v>116.6056870536144</v>
       </c>
       <c r="M14" t="n">
-        <v>123.0658373688389</v>
+        <v>126.9046812592338</v>
       </c>
       <c r="N14" t="n">
-        <v>115.7084566568807</v>
-      </c>
-      <c r="O14" t="n">
-        <v>104.9929815312719</v>
-      </c>
-      <c r="P14" t="n">
-        <v>95.01728148366979</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>110.9086982243956</v>
+        <v>119.7498298778816</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>105.0847073411071</v>
       </c>
     </row>
     <row r="15">
@@ -1017,52 +1001,50 @@
         <v>1993</v>
       </c>
       <c r="B15" t="n">
-        <v>94.15729018829656</v>
+        <v>91.24185309400342</v>
       </c>
       <c r="C15" t="n">
-        <v>118.9360459448427</v>
+        <v>111.0387158812622</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1251740892478009</v>
+        <v>0.1236795709150767</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4468708505655035</v>
+        <v>0.4424314561133058</v>
       </c>
       <c r="F15" t="n">
-        <v>87.29938365532304</v>
+        <v>86.50850781722033</v>
       </c>
       <c r="G15" t="n">
-        <v>69.35703313525948</v>
+        <v>68.48863369383092</v>
       </c>
       <c r="H15" t="n">
-        <v>86.89874366665923</v>
+        <v>85.7529889729219</v>
       </c>
       <c r="I15" t="n">
-        <v>81.66281936495106</v>
+        <v>78.03879147679142</v>
       </c>
       <c r="J15" t="n">
-        <v>86.4074365744362</v>
+        <v>87.00166483157041</v>
       </c>
       <c r="K15" t="n">
-        <v>72.33631835446074</v>
+        <v>74.11129703565709</v>
       </c>
       <c r="L15" t="n">
-        <v>61.35493744245302</v>
+        <v>62.75961108165072</v>
       </c>
       <c r="M15" t="n">
-        <v>68.97219075389394</v>
+        <v>65.91374181131931</v>
       </c>
       <c r="N15" t="n">
-        <v>65.01883138779888</v>
-      </c>
-      <c r="O15" t="n">
-        <v>103.7310516945815</v>
-      </c>
-      <c r="P15" t="n">
-        <v>96.60444621169466</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>105.5509729799443</v>
+        <v>60.69878357802661</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>106.292430229092</v>
       </c>
     </row>
     <row r="16">
@@ -1070,52 +1052,50 @@
         <v>1994</v>
       </c>
       <c r="B16" t="n">
-        <v>94.9744463530062</v>
+        <v>94.2172027319012</v>
       </c>
       <c r="C16" t="n">
-        <v>112.2836682764047</v>
+        <v>110.0922093347588</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1209209382115584</v>
+        <v>0.1209095154980509</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4531005461079559</v>
+        <v>0.4524136728835484</v>
       </c>
       <c r="F16" t="n">
-        <v>92.60819131272451</v>
+        <v>94.37346815085155</v>
       </c>
       <c r="G16" t="n">
-        <v>74.80470242191774</v>
+        <v>74.6622356124513</v>
       </c>
       <c r="H16" t="n">
-        <v>95.5653082382849</v>
+        <v>99.47431364769693</v>
       </c>
       <c r="I16" t="n">
-        <v>92.50513843144356</v>
+        <v>93.83970352632241</v>
       </c>
       <c r="J16" t="n">
-        <v>99.29578219224339</v>
+        <v>96.70398463115662</v>
       </c>
       <c r="K16" t="n">
-        <v>83.40354318275527</v>
+        <v>82.93882067981416</v>
       </c>
       <c r="L16" t="n">
-        <v>72.02208120810693</v>
+        <v>68.7508517715326</v>
       </c>
       <c r="M16" t="n">
-        <v>76.70660262403973</v>
+        <v>76.42984961855103</v>
       </c>
       <c r="N16" t="n">
-        <v>61.17855128769957</v>
-      </c>
-      <c r="O16" t="n">
-        <v>106.1198910608174</v>
-      </c>
-      <c r="P16" t="n">
-        <v>97.6503192622544</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>109.330037007264</v>
+        <v>66.30293046212212</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>110.2887609505475</v>
       </c>
     </row>
     <row r="17">
@@ -1123,52 +1103,50 @@
         <v>1995</v>
       </c>
       <c r="B17" t="n">
-        <v>88.86460620077547</v>
+        <v>91.37096789692244</v>
       </c>
       <c r="C17" t="n">
-        <v>105.4585704043334</v>
+        <v>108.3883298076951</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1184500970789838</v>
+        <v>0.1192948853893315</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5031045459456182</v>
+        <v>0.500847134232309</v>
       </c>
       <c r="F17" t="n">
-        <v>108.4671166996551</v>
+        <v>109.92302104475</v>
       </c>
       <c r="G17" t="n">
-        <v>82.23540385273684</v>
+        <v>83.54656471341154</v>
       </c>
       <c r="H17" t="n">
-        <v>119.8679676058009</v>
+        <v>119.2258573841161</v>
       </c>
       <c r="I17" t="n">
-        <v>104.772722441572</v>
+        <v>105.4365606009522</v>
       </c>
       <c r="J17" t="n">
-        <v>115.0473940039146</v>
+        <v>110.9485356927204</v>
       </c>
       <c r="K17" t="n">
-        <v>99.66291854607307</v>
+        <v>99.13831195755719</v>
       </c>
       <c r="L17" t="n">
-        <v>89.23658938049758</v>
+        <v>96.41711402843191</v>
       </c>
       <c r="M17" t="n">
-        <v>96.84388893788149</v>
+        <v>90.42773477195989</v>
       </c>
       <c r="N17" t="n">
-        <v>97.32180157547961</v>
-      </c>
-      <c r="O17" t="n">
-        <v>106.6065835725907</v>
-      </c>
-      <c r="P17" t="n">
-        <v>98.73366132997305</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>104.5523174539896</v>
+        <v>94.4251384115552</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>103.5987869865801</v>
       </c>
     </row>
     <row r="18">
@@ -1176,52 +1154,50 @@
         <v>1996</v>
       </c>
       <c r="B18" t="n">
-        <v>86.76058156446996</v>
+        <v>83.56406288300619</v>
       </c>
       <c r="C18" t="n">
-        <v>103.8236168607112</v>
+        <v>108.0335310885547</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1150350141871481</v>
+        <v>0.1143209382115584</v>
       </c>
       <c r="E18" t="n">
-        <v>0.531682472578522</v>
+        <v>0.5121755461079559</v>
       </c>
       <c r="F18" t="n">
-        <v>108.66280567015</v>
+        <v>109.0109399827245</v>
       </c>
       <c r="G18" t="n">
-        <v>76.51859533052728</v>
+        <v>77.40486462191774</v>
       </c>
       <c r="H18" t="n">
-        <v>123.7495747360167</v>
+        <v>129.1620748482849</v>
       </c>
       <c r="I18" t="n">
-        <v>105.9006657103156</v>
+        <v>107.8783369314436</v>
       </c>
       <c r="J18" t="n">
-        <v>102.2394060297592</v>
+        <v>102.7823347322434</v>
       </c>
       <c r="K18" t="n">
-        <v>109.0599260468523</v>
+        <v>110.0279053527553</v>
       </c>
       <c r="L18" t="n">
-        <v>95.04700214825716</v>
+        <v>96.07427947810692</v>
       </c>
       <c r="M18" t="n">
-        <v>91.87199681441625</v>
+        <v>96.62701483403973</v>
       </c>
       <c r="N18" t="n">
-        <v>91.93903259730317</v>
-      </c>
-      <c r="O18" t="n">
-        <v>104.632821888806</v>
-      </c>
-      <c r="P18" t="n">
-        <v>101.58442465916</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>99.70833362604215</v>
+        <v>88.74138091769956</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>104.6961731608174</v>
       </c>
     </row>
     <row r="19">
@@ -1229,52 +1205,50 @@
         <v>1997</v>
       </c>
       <c r="B19" t="n">
-        <v>83.768585441681</v>
+        <v>80.41377571423865</v>
       </c>
       <c r="C19" t="n">
-        <v>103.6785499563799</v>
+        <v>105.6520283723797</v>
       </c>
       <c r="D19" t="n">
-        <v>0.109053362389166</v>
+        <v>0.1094089294919681</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5579287931910289</v>
+        <v>0.55185423995659</v>
       </c>
       <c r="F19" t="n">
-        <v>115.4427190955786</v>
+        <v>115.9459819522248</v>
       </c>
       <c r="G19" t="n">
-        <v>77.29417568120843</v>
+        <v>79.05199656391659</v>
       </c>
       <c r="H19" t="n">
-        <v>139.9149094451641</v>
+        <v>137.1770838481887</v>
       </c>
       <c r="I19" t="n">
-        <v>118.3848393293406</v>
+        <v>118.4658245002382</v>
       </c>
       <c r="J19" t="n">
-        <v>111.2692805933313</v>
+        <v>110.1976589530529</v>
       </c>
       <c r="K19" t="n">
-        <v>126.8687246837511</v>
+        <v>124.7329067862402</v>
       </c>
       <c r="L19" t="n">
-        <v>104.0394721687832</v>
+        <v>104.3998244339844</v>
       </c>
       <c r="M19" t="n">
-        <v>112.8887577027053</v>
+        <v>116.6733031230204</v>
       </c>
       <c r="N19" t="n">
-        <v>99.73041831432991</v>
-      </c>
-      <c r="O19" t="n">
-        <v>101.0510542549639</v>
-      </c>
-      <c r="P19" t="n">
-        <v>100.9458509705207</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>100.5663714967373</v>
+        <v>92.88379762394206</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>104.3144319292543</v>
       </c>
     </row>
     <row r="20">
@@ -1282,52 +1256,50 @@
         <v>1998</v>
       </c>
       <c r="B20" t="n">
-        <v>73.8761140768793</v>
+        <v>77.26073024032382</v>
       </c>
       <c r="C20" t="n">
-        <v>100.3681505163214</v>
+        <v>104.2466008929035</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1072084330232334</v>
+        <v>0.1047414151868081</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5774083335765305</v>
+        <v>0.5775006551499963</v>
       </c>
       <c r="F20" t="n">
-        <v>80.71369979180152</v>
+        <v>83.76734636017925</v>
       </c>
       <c r="G20" t="n">
-        <v>54.86703135412365</v>
+        <v>52.99973488484348</v>
       </c>
       <c r="H20" t="n">
-        <v>102.9568304434592</v>
+        <v>103.1439451092197</v>
       </c>
       <c r="I20" t="n">
-        <v>86.10098872464822</v>
+        <v>88.43997220821834</v>
       </c>
       <c r="J20" t="n">
-        <v>80.26448980229478</v>
+        <v>76.93828137572029</v>
       </c>
       <c r="K20" t="n">
-        <v>96.14317340045729</v>
+        <v>95.54758615892165</v>
       </c>
       <c r="L20" t="n">
-        <v>65.26722877354274</v>
+        <v>57.12558975385223</v>
       </c>
       <c r="M20" t="n">
-        <v>70.55155498801059</v>
+        <v>66.74116349869961</v>
       </c>
       <c r="N20" t="n">
-        <v>60.51085781792883</v>
-      </c>
-      <c r="O20" t="n">
-        <v>101.4290011727371</v>
-      </c>
-      <c r="P20" t="n">
-        <v>101.1340608515007</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>98.31316214218228</v>
+        <v>61.67369582498155</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>100.6471388837142</v>
       </c>
     </row>
     <row r="21">
@@ -1335,52 +1307,50 @@
         <v>1999</v>
       </c>
       <c r="B21" t="n">
-        <v>65.69856252693853</v>
+        <v>68.7378510187186</v>
       </c>
       <c r="C21" t="n">
-        <v>100.2749263634495</v>
+        <v>96.6488337404863</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1062927230762759</v>
+        <v>0.1030609769813299</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5867036467331862</v>
+        <v>0.5943101288271408</v>
       </c>
       <c r="F21" t="n">
-        <v>82.02092112960842</v>
+        <v>83.49187551933827</v>
       </c>
       <c r="G21" t="n">
-        <v>57.99092199793885</v>
+        <v>56.51165097384001</v>
       </c>
       <c r="H21" t="n">
-        <v>92.29844734765609</v>
+        <v>95.27499813326502</v>
       </c>
       <c r="I21" t="n">
-        <v>90.9878673729998</v>
+        <v>89.25293706923078</v>
       </c>
       <c r="J21" t="n">
-        <v>91.77816444465569</v>
+        <v>88.48765839248854</v>
       </c>
       <c r="K21" t="n">
-        <v>88.14863574558743</v>
+        <v>87.57808276598969</v>
       </c>
       <c r="L21" t="n">
-        <v>56.28715496155833</v>
+        <v>54.0652069201151</v>
       </c>
       <c r="M21" t="n">
-        <v>55.44519589812894</v>
+        <v>54.01407706477575</v>
       </c>
       <c r="N21" t="n">
-        <v>55.53502712806667</v>
-      </c>
-      <c r="O21" t="n">
-        <v>100.8430222313807</v>
-      </c>
-      <c r="P21" t="n">
-        <v>100.4077736269552</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>95.54500825349947</v>
+        <v>54.30012229169567</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>100.7576875723506</v>
       </c>
     </row>
     <row r="22">
@@ -1388,52 +1358,50 @@
         <v>2000</v>
       </c>
       <c r="B22" t="n">
-        <v>62.310439731422</v>
+        <v>62.34081101864294</v>
       </c>
       <c r="C22" t="n">
-        <v>97.72910538677046</v>
+        <v>97.88604080346842</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0986383546804796</v>
+        <v>0.1031617538242263</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6253010605194658</v>
+        <v>0.5902315490595235</v>
       </c>
       <c r="F22" t="n">
-        <v>83.68118176581565</v>
+        <v>88.84504320356874</v>
       </c>
       <c r="G22" t="n">
-        <v>59.24174217771645</v>
+        <v>58.3569404648162</v>
       </c>
       <c r="H22" t="n">
-        <v>101.2145052029143</v>
+        <v>98.39089212527405</v>
       </c>
       <c r="I22" t="n">
-        <v>90.49838622957316</v>
+        <v>90.17429247120695</v>
       </c>
       <c r="J22" t="n">
-        <v>85.97011239687214</v>
+        <v>85.34525824195524</v>
       </c>
       <c r="K22" t="n">
-        <v>93.63039262422311</v>
+        <v>91.59916054386824</v>
       </c>
       <c r="L22" t="n">
-        <v>58.27892402921213</v>
+        <v>57.88556031281803</v>
       </c>
       <c r="M22" t="n">
-        <v>63.62078158403844</v>
+        <v>64.55206846709069</v>
       </c>
       <c r="N22" t="n">
-        <v>55.82957455692438</v>
-      </c>
-      <c r="O22" t="n">
-        <v>99.73281667076742</v>
-      </c>
-      <c r="P22" t="n">
-        <v>100.6238672213727</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>94.51155193146182</v>
+        <v>54.48771453083234</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>101.4688773570647</v>
       </c>
     </row>
     <row r="23">
@@ -1441,52 +1409,50 @@
         <v>2001</v>
       </c>
       <c r="B23" t="n">
-        <v>55.91372168972527</v>
+        <v>58.0875371802251</v>
       </c>
       <c r="C23" t="n">
-        <v>92.60119945574988</v>
+        <v>91.73062967370967</v>
       </c>
       <c r="D23" t="n">
-        <v>0.09724356736269982</v>
+        <v>0.09815919883426689</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6076635612893857</v>
+        <v>0.6168360924540384</v>
       </c>
       <c r="F23" t="n">
-        <v>79.39562296625776</v>
+        <v>82.08539774199983</v>
       </c>
       <c r="G23" t="n">
-        <v>59.74494522543952</v>
+        <v>60.20772092952527</v>
       </c>
       <c r="H23" t="n">
-        <v>90.14635011900894</v>
+        <v>87.83131744408941</v>
       </c>
       <c r="I23" t="n">
-        <v>83.63104280805415</v>
+        <v>83.54619184867087</v>
       </c>
       <c r="J23" t="n">
-        <v>82.04472397691477</v>
+        <v>84.26337086362214</v>
       </c>
       <c r="K23" t="n">
-        <v>85.42372191910415</v>
+        <v>86.03797350012049</v>
       </c>
       <c r="L23" t="n">
-        <v>58.85012743206968</v>
+        <v>61.71624378659648</v>
       </c>
       <c r="M23" t="n">
-        <v>77.57125184207179</v>
+        <v>81.08394431462614</v>
       </c>
       <c r="N23" t="n">
-        <v>52.46113704718163</v>
-      </c>
-      <c r="O23" t="n">
-        <v>99.81217168103628</v>
-      </c>
-      <c r="P23" t="n">
-        <v>99.9432841482441</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>97.37044414251392</v>
+        <v>56.4879298816039</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>99.38221216867542</v>
       </c>
     </row>
     <row r="24">
@@ -1494,52 +1460,50 @@
         <v>2002</v>
       </c>
       <c r="B24" t="n">
-        <v>53.85392445472078</v>
+        <v>53.28301724811124</v>
       </c>
       <c r="C24" t="n">
-        <v>70.64118186435488</v>
+        <v>70.54217026191435</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0927197779343486</v>
+        <v>0.09234600409961904</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6133759536712966</v>
+        <v>0.6355042706040606</v>
       </c>
       <c r="F24" t="n">
-        <v>78.33648559620812</v>
+        <v>79.72478265229329</v>
       </c>
       <c r="G24" t="n">
-        <v>53.2547528505248</v>
+        <v>54.5763431098521</v>
       </c>
       <c r="H24" t="n">
-        <v>94.97068718581033</v>
+        <v>97.08912617008896</v>
       </c>
       <c r="I24" t="n">
-        <v>78.03086128330283</v>
+        <v>79.38278506049923</v>
       </c>
       <c r="J24" t="n">
-        <v>74.49321734758165</v>
+        <v>74.78933231142702</v>
       </c>
       <c r="K24" t="n">
-        <v>86.95009816469062</v>
+        <v>83.95774205173939</v>
       </c>
       <c r="L24" t="n">
-        <v>61.82486626494952</v>
+        <v>62.69428381278079</v>
       </c>
       <c r="M24" t="n">
-        <v>66.76466227302083</v>
+        <v>65.53941758271031</v>
       </c>
       <c r="N24" t="n">
-        <v>62.8636435455403</v>
-      </c>
-      <c r="O24" t="n">
-        <v>99.82835089856009</v>
-      </c>
-      <c r="P24" t="n">
-        <v>100.0613682924857</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>94.7707386649862</v>
+        <v>61.66707357681928</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>100.961317106002</v>
       </c>
     </row>
     <row r="25">
@@ -1547,52 +1511,50 @@
         <v>2003</v>
       </c>
       <c r="B25" t="n">
-        <v>52.22843028233342</v>
+        <v>50.54473534952777</v>
       </c>
       <c r="C25" t="n">
-        <v>61.97073279418062</v>
+        <v>68.68504936037652</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08909055856639979</v>
+        <v>0.08715169542807405</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6395109589708858</v>
+        <v>0.6214803577377979</v>
       </c>
       <c r="F25" t="n">
-        <v>97.47675983022768</v>
+        <v>96.99470950540969</v>
       </c>
       <c r="G25" t="n">
-        <v>67.09373110503763</v>
+        <v>66.89275519252304</v>
       </c>
       <c r="H25" t="n">
-        <v>117.2046722881313</v>
+        <v>113.908623310319</v>
       </c>
       <c r="I25" t="n">
-        <v>95.5029772620544</v>
+        <v>97.72744468884038</v>
       </c>
       <c r="J25" t="n">
-        <v>90.62495968491196</v>
+        <v>89.01411561851516</v>
       </c>
       <c r="K25" t="n">
-        <v>104.2080249641946</v>
+        <v>102.4535381341414</v>
       </c>
       <c r="L25" t="n">
-        <v>81.43382016951259</v>
+        <v>77.18841759120096</v>
       </c>
       <c r="M25" t="n">
-        <v>81.98437003301157</v>
+        <v>82.28647203136934</v>
       </c>
       <c r="N25" t="n">
-        <v>73.75842138599769</v>
-      </c>
-      <c r="O25" t="n">
-        <v>99.70946503274314</v>
-      </c>
-      <c r="P25" t="n">
-        <v>100.0772198220592</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>93.1197365420219</v>
+        <v>77.41953940296538</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>100.2238088129444</v>
       </c>
     </row>
     <row r="26">
@@ -1600,52 +1562,50 @@
         <v>2004</v>
       </c>
       <c r="B26" t="n">
-        <v>46.93119403099388</v>
+        <v>46.80919596972527</v>
       </c>
       <c r="C26" t="n">
-        <v>48.21075982505451</v>
+        <v>47.10526634302757</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08597632250915316</v>
+        <v>0.08611023402936649</v>
       </c>
       <c r="E26" t="n">
-        <v>0.664357474004365</v>
+        <v>0.6386635612893857</v>
       </c>
       <c r="F26" t="n">
-        <v>101.13448965806</v>
+        <v>98.21842046625777</v>
       </c>
       <c r="G26" t="n">
-        <v>70.45775388800288</v>
+        <v>71.44170971543952</v>
       </c>
       <c r="H26" t="n">
-        <v>112.7193538237025</v>
+        <v>115.1840275890089</v>
       </c>
       <c r="I26" t="n">
-        <v>96.62321809747445</v>
+        <v>95.03122283805413</v>
       </c>
       <c r="J26" t="n">
-        <v>86.63220309989072</v>
+        <v>88.17863195691476</v>
       </c>
       <c r="K26" t="n">
-        <v>104.9873764335675</v>
+        <v>102.3905310391042</v>
       </c>
       <c r="L26" t="n">
-        <v>79.76035848589331</v>
+        <v>74.48367556206968</v>
       </c>
       <c r="M26" t="n">
-        <v>83.54143552618476</v>
+        <v>81.37988205207178</v>
       </c>
       <c r="N26" t="n">
-        <v>71.82293191351097</v>
-      </c>
-      <c r="O26" t="n">
-        <v>101.5595045774373</v>
-      </c>
-      <c r="P26" t="n">
-        <v>102.5584842000783</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>95.19181770925447</v>
+        <v>73.82954155718163</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>99.77732858103629</v>
       </c>
     </row>
     <row r="27">
@@ -1653,52 +1613,50 @@
         <v>2005</v>
       </c>
       <c r="B27" t="n">
-        <v>52.81406876405626</v>
+        <v>56.31665041562935</v>
       </c>
       <c r="C27" t="n">
-        <v>42.18219169217647</v>
+        <v>47.04378750072346</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08163208786437338</v>
+        <v>0.0832358468355229</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6554280739191131</v>
+        <v>0.653249061687064</v>
       </c>
       <c r="F27" t="n">
-        <v>90.48861987217897</v>
+        <v>91.1977127932124</v>
       </c>
       <c r="G27" t="n">
-        <v>69.00773182033548</v>
+        <v>67.05876858533178</v>
       </c>
       <c r="H27" t="n">
-        <v>97.10099759015706</v>
+        <v>99.36245433528771</v>
       </c>
       <c r="I27" t="n">
-        <v>90.04301335215834</v>
+        <v>89.80987239906612</v>
       </c>
       <c r="J27" t="n">
-        <v>88.84639717170049</v>
+        <v>89.21502003746892</v>
       </c>
       <c r="K27" t="n">
-        <v>91.75512400584533</v>
+        <v>89.57675102152544</v>
       </c>
       <c r="L27" t="n">
-        <v>68.52480057222269</v>
+        <v>68.13868078270411</v>
       </c>
       <c r="M27" t="n">
-        <v>73.52667982740549</v>
+        <v>79.64854261849224</v>
       </c>
       <c r="N27" t="n">
-        <v>60.68352517133953</v>
-      </c>
-      <c r="O27" t="n">
-        <v>101.0763489548774</v>
-      </c>
-      <c r="P27" t="n">
-        <v>103.8950801307267</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>89.9702274962317</v>
+        <v>63.55892176886411</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>100.0803019148369</v>
       </c>
     </row>
     <row r="28">
@@ -1706,52 +1664,50 @@
         <v>2006</v>
       </c>
       <c r="B28" t="n">
-        <v>69.7967167886101</v>
+        <v>68.2139240457123</v>
       </c>
       <c r="C28" t="n">
-        <v>53.11833681584134</v>
+        <v>51.9071268849715</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08012987355616717</v>
+        <v>0.07833272492447323</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6659776864807427</v>
+        <v>0.6653992740102509</v>
       </c>
       <c r="F28" t="n">
-        <v>103.1905511375624</v>
+        <v>99.96122109768913</v>
       </c>
       <c r="G28" t="n">
-        <v>82.86025974899223</v>
+        <v>79.82855974826359</v>
       </c>
       <c r="H28" t="n">
-        <v>99.78545262915912</v>
+        <v>100.374954156479</v>
       </c>
       <c r="I28" t="n">
-        <v>94.77580708169643</v>
+        <v>94.02102296994734</v>
       </c>
       <c r="J28" t="n">
-        <v>95.92274594914372</v>
+        <v>97.39009149803336</v>
       </c>
       <c r="K28" t="n">
-        <v>92.72427662249774</v>
+        <v>92.05962696495408</v>
       </c>
       <c r="L28" t="n">
-        <v>67.99723797990289</v>
+        <v>74.25912306955681</v>
       </c>
       <c r="M28" t="n">
-        <v>91.42357480343453</v>
+        <v>88.07534984713217</v>
       </c>
       <c r="N28" t="n">
-        <v>63.74828974122638</v>
-      </c>
-      <c r="O28" t="n">
-        <v>96.92371777995426</v>
-      </c>
-      <c r="P28" t="n">
-        <v>103.2077059963331</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>86.31914733267004</v>
+        <v>63.37285853670965</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>99.13203009996293</v>
       </c>
     </row>
     <row r="29">
@@ -1759,52 +1715,50 @@
         <v>2007</v>
       </c>
       <c r="B29" t="n">
-        <v>69.61515732358393</v>
+        <v>74.13592768425892</v>
       </c>
       <c r="C29" t="n">
-        <v>53.41657039141219</v>
+        <v>49.84115790583309</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07702657624498778</v>
+        <v>0.07262012402564751</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6763802731325974</v>
+        <v>0.669287949752104</v>
       </c>
       <c r="F29" t="n">
-        <v>71.40700746872504</v>
+        <v>65.23397945913587</v>
       </c>
       <c r="G29" t="n">
-        <v>50.96769701314722</v>
+        <v>51.99212853989903</v>
       </c>
       <c r="H29" t="n">
-        <v>69.67760995697695</v>
+        <v>71.71303573520856</v>
       </c>
       <c r="I29" t="n">
-        <v>63.23179459753215</v>
+        <v>63.56002587930624</v>
       </c>
       <c r="J29" t="n">
-        <v>60.34352935824629</v>
+        <v>60.26648156849227</v>
       </c>
       <c r="K29" t="n">
-        <v>66.42198379260702</v>
+        <v>69.52127193003379</v>
       </c>
       <c r="L29" t="n">
-        <v>44.90439042764983</v>
+        <v>50.96497022114094</v>
       </c>
       <c r="M29" t="n">
-        <v>61.66535227827835</v>
+        <v>60.54163521837283</v>
       </c>
       <c r="N29" t="n">
-        <v>41.18854116648117</v>
-      </c>
-      <c r="O29" t="n">
-        <v>98.31921337242257</v>
-      </c>
-      <c r="P29" t="n">
-        <v>102.7242294632674</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>87.39928993181907</v>
+        <v>42.00768409933541</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>98.11709261968844</v>
       </c>
     </row>
     <row r="30">
@@ -1812,48 +1766,46 @@
         <v>2008</v>
       </c>
       <c r="B30" t="n">
-        <v>76.43427640172202</v>
+        <v>74.95193159722979</v>
       </c>
       <c r="C30" t="n">
-        <v>43.74951881759857</v>
+        <v>50.52306134093314</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>62.37150409688991</v>
+        <v>61.17488865311972</v>
       </c>
       <c r="G30" t="n">
-        <v>47.18143534875258</v>
+        <v>48.20044633143925</v>
       </c>
       <c r="H30" t="n">
-        <v>70.7020012803048</v>
+        <v>71.59812293346238</v>
       </c>
       <c r="I30" t="n">
-        <v>57.42348005176676</v>
+        <v>60.66000959068205</v>
       </c>
       <c r="J30" t="n">
-        <v>53.82672129020182</v>
+        <v>51.1180920921377</v>
       </c>
       <c r="K30" t="n">
-        <v>61.22033086563521</v>
+        <v>61.92801733644098</v>
       </c>
       <c r="L30" t="n">
-        <v>43.83452745944059</v>
+        <v>44.95691517399025</v>
       </c>
       <c r="M30" t="n">
-        <v>52.63723320031679</v>
+        <v>55.50503907154683</v>
       </c>
       <c r="N30" t="n">
-        <v>44.57723352427354</v>
-      </c>
-      <c r="O30" t="n">
-        <v>95.8626535266431</v>
-      </c>
-      <c r="P30" t="n">
-        <v>99.73855852721991</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>88.49203257570983</v>
+        <v>39.70582573428973</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>96.53078936341942</v>
       </c>
     </row>
     <row r="31">
@@ -1861,48 +1813,46 @@
         <v>2009</v>
       </c>
       <c r="B31" t="n">
-        <v>95.01159421582548</v>
+        <v>93.25547827456741</v>
       </c>
       <c r="C31" t="n">
-        <v>63.37848123901014</v>
+        <v>63.56263683659117</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>84.07134073460406</v>
+        <v>86.11467024552252</v>
       </c>
       <c r="G31" t="n">
-        <v>58.76229089973124</v>
+        <v>58.10420603889131</v>
       </c>
       <c r="H31" t="n">
-        <v>99.26828001279512</v>
+        <v>96.55424366840347</v>
       </c>
       <c r="I31" t="n">
-        <v>73.1633573420287</v>
+        <v>78.8685508986441</v>
       </c>
       <c r="J31" t="n">
-        <v>62.33876167794243</v>
+        <v>65.70316619272398</v>
       </c>
       <c r="K31" t="n">
-        <v>91.68545414662681</v>
+        <v>88.25089453708557</v>
       </c>
       <c r="L31" t="n">
-        <v>64.07425287191708</v>
+        <v>63.88584895420038</v>
       </c>
       <c r="M31" t="n">
-        <v>64.36217327911892</v>
+        <v>65.20236469302716</v>
       </c>
       <c r="N31" t="n">
-        <v>61.37372270762924</v>
-      </c>
-      <c r="O31" t="n">
-        <v>94.19712204597438</v>
-      </c>
-      <c r="P31" t="n">
-        <v>99.75480265089206</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>88.45444531645816</v>
+        <v>62.58964321129962</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>93.91997834282429</v>
       </c>
     </row>
     <row r="32">
@@ -1910,48 +1860,46 @@
         <v>2010</v>
       </c>
       <c r="B32" t="n">
-        <v>101.9879060291729</v>
+        <v>106.0113343376942</v>
       </c>
       <c r="C32" t="n">
-        <v>76.05392559732371</v>
+        <v>82.40617442340663</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>98.7863775008187</v>
+        <v>101.0922728138239</v>
       </c>
       <c r="G32" t="n">
-        <v>75.77144221266914</v>
+        <v>79.11794280415481</v>
       </c>
       <c r="H32" t="n">
-        <v>103.6564027352844</v>
+        <v>102.9701659102135</v>
       </c>
       <c r="I32" t="n">
-        <v>84.68207005130303</v>
+        <v>87.49928503134699</v>
       </c>
       <c r="J32" t="n">
-        <v>82.60909433532613</v>
+        <v>81.46416713508938</v>
       </c>
       <c r="K32" t="n">
-        <v>94.25513687622116</v>
+        <v>89.9681424845288</v>
       </c>
       <c r="L32" t="n">
-        <v>78.45238300378482</v>
+        <v>76.0921344210855</v>
       </c>
       <c r="M32" t="n">
-        <v>107.9980734811571</v>
+        <v>99.89087526271136</v>
       </c>
       <c r="N32" t="n">
-        <v>67.713506011532</v>
-      </c>
-      <c r="O32" t="n">
-        <v>90.2768814238312</v>
-      </c>
-      <c r="P32" t="n">
-        <v>97.18429088294457</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>84.22334351740388</v>
+        <v>67.01394923609749</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>92.0721417826242</v>
       </c>
     </row>
     <row r="33">
@@ -1959,48 +1907,46 @@
         <v>2011</v>
       </c>
       <c r="B33" t="n">
-        <v>102.5839406667124</v>
+        <v>107.2524984507781</v>
       </c>
       <c r="C33" t="n">
-        <v>65.12651177423166</v>
+        <v>65.74614316010675</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>96.83237421030468</v>
+        <v>92.50664504268475</v>
       </c>
       <c r="G33" t="n">
-        <v>79.233041701803</v>
+        <v>76.87688811806892</v>
       </c>
       <c r="H33" t="n">
-        <v>92.79212713012264</v>
+        <v>96.63477268106755</v>
       </c>
       <c r="I33" t="n">
-        <v>85.72603103249043</v>
+        <v>84.77665673387071</v>
       </c>
       <c r="J33" t="n">
-        <v>83.06471252795698</v>
+        <v>80.4846456014932</v>
       </c>
       <c r="K33" t="n">
-        <v>83.4763333342926</v>
+        <v>84.12254606413218</v>
       </c>
       <c r="L33" t="n">
-        <v>70.37436042375705</v>
+        <v>68.94434632197323</v>
       </c>
       <c r="M33" t="n">
-        <v>98.58338115159151</v>
+        <v>102.1165126018947</v>
       </c>
       <c r="N33" t="n">
-        <v>59.75649162886932</v>
-      </c>
-      <c r="O33" t="n">
-        <v>87.61130790593997</v>
-      </c>
-      <c r="P33" t="n">
-        <v>95.76686374433574</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>79.31965144067978</v>
+        <v>60.39815426937196</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>87.48744557932721</v>
       </c>
     </row>
     <row r="34">
@@ -2008,48 +1954,46 @@
         <v>2012</v>
       </c>
       <c r="B34" t="n">
-        <v>109.9157290152715</v>
+        <v>109.410345091722</v>
       </c>
       <c r="C34" t="n">
-        <v>63.88029089533952</v>
+        <v>63.52493868931837</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>56.43146706253509</v>
+        <v>53.98588071688992</v>
       </c>
       <c r="G34" t="n">
-        <v>40.14893399561367</v>
+        <v>41.92549615875258</v>
       </c>
       <c r="H34" t="n">
-        <v>61.36415456827816</v>
+        <v>60.00700989030479</v>
       </c>
       <c r="I34" t="n">
-        <v>52.07710395440981</v>
+        <v>49.61584937176676</v>
       </c>
       <c r="J34" t="n">
-        <v>44.9960177338723</v>
+        <v>47.84118515020182</v>
       </c>
       <c r="K34" t="n">
-        <v>54.05125139091695</v>
+        <v>51.48818771563521</v>
       </c>
       <c r="L34" t="n">
-        <v>38.82014853960254</v>
+        <v>39.03899469944059</v>
       </c>
       <c r="M34" t="n">
-        <v>55.70020299438972</v>
+        <v>51.62612749031679</v>
       </c>
       <c r="N34" t="n">
-        <v>32.71125020723473</v>
-      </c>
-      <c r="O34" t="n">
-        <v>84.07311856150484</v>
-      </c>
-      <c r="P34" t="n">
-        <v>94.51107606327579</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>76.05589293507316</v>
+        <v>38.21447019427354</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>86.16552113664311</v>
       </c>
     </row>
     <row r="35">
@@ -2061,40 +2005,38 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>90.07600167314767</v>
+        <v>91.19503380598813</v>
       </c>
       <c r="G35" t="n">
-        <v>59.52571380141672</v>
+        <v>61.88613560238399</v>
       </c>
       <c r="H35" t="n">
-        <v>108.3429232252438</v>
+        <v>108.6044729884323</v>
       </c>
       <c r="I35" t="n">
-        <v>81.46031598336492</v>
+        <v>80.46702759629733</v>
       </c>
       <c r="J35" t="n">
-        <v>63.68121291653765</v>
+        <v>64.74718749304617</v>
       </c>
       <c r="K35" t="n">
-        <v>99.5274317457461</v>
+        <v>96.41434271409895</v>
       </c>
       <c r="L35" t="n">
-        <v>62.23449466625472</v>
+        <v>57.17076602041475</v>
       </c>
       <c r="M35" t="n">
-        <v>58.30374019034209</v>
+        <v>62.78163386339907</v>
       </c>
       <c r="N35" t="n">
-        <v>64.15609075482716</v>
-      </c>
-      <c r="O35" t="n">
-        <v>82.96689053000853</v>
-      </c>
-      <c r="P35" t="n">
-        <v>96.72684852828627</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>75.4278004595642</v>
+        <v>65.78865941809083</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>83.96828836975399</v>
       </c>
     </row>
     <row r="36">
@@ -2106,40 +2048,38 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>91.83954469797315</v>
+        <v>91.01856575200131</v>
       </c>
       <c r="G36" t="n">
-        <v>66.29075424863824</v>
+        <v>65.86921063345603</v>
       </c>
       <c r="H36" t="n">
-        <v>101.9043927336542</v>
+        <v>98.25488238356957</v>
       </c>
       <c r="I36" t="n">
-        <v>79.10118926511053</v>
+        <v>79.67359102426799</v>
       </c>
       <c r="J36" t="n">
-        <v>68.13020117630191</v>
+        <v>64.62625350481754</v>
       </c>
       <c r="K36" t="n">
-        <v>94.52807255449279</v>
+        <v>91.80577634533546</v>
       </c>
       <c r="L36" t="n">
-        <v>58.18154916122438</v>
+        <v>56.2050947555765</v>
       </c>
       <c r="M36" t="n">
-        <v>61.63823903710549</v>
+        <v>60.09550421691118</v>
       </c>
       <c r="N36" t="n">
-        <v>55.20816388583431</v>
-      </c>
-      <c r="O36" t="n">
-        <v>82.14222354237374</v>
-      </c>
-      <c r="P36" t="n">
-        <v>98.85619986265002</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>68.20155705586515</v>
+        <v>59.59532840560902</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>83.63657870927955</v>
       </c>
     </row>
     <row r="37">
@@ -2151,40 +2091,46 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>83.84757113863321</v>
+        <v>84.37712595169623</v>
       </c>
       <c r="G37" t="n">
-        <v>57.21016499117432</v>
+        <v>58.34567826162651</v>
       </c>
       <c r="H37" t="n">
-        <v>90.97330486588753</v>
+        <v>93.13079931825901</v>
       </c>
       <c r="I37" t="n">
-        <v>71.59870871865289</v>
+        <v>72.90204181449245</v>
       </c>
       <c r="J37" t="n">
-        <v>57.06704719470916</v>
+        <v>58.87931111062444</v>
       </c>
       <c r="K37" t="n">
-        <v>87.06047898887523</v>
+        <v>85.3860534805375</v>
       </c>
       <c r="L37" t="n">
-        <v>53.33300660804395</v>
+        <v>55.15599907544444</v>
       </c>
       <c r="M37" t="n">
-        <v>58.87750278016291</v>
+        <v>59.41422200776726</v>
       </c>
       <c r="N37" t="n">
-        <v>54.56998711563971</v>
+        <v>51.08910992739227</v>
       </c>
       <c r="O37" t="n">
-        <v>81.08016055903263</v>
+        <v>99.8</v>
       </c>
       <c r="P37" t="n">
-        <v>102.3147740619547</v>
+        <v>99.77</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.23066852814851</v>
+        <v>99.56999999999999</v>
+      </c>
+      <c r="R37" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="S37" t="n">
+        <v>81.96944059451484</v>
       </c>
     </row>
     <row r="38">
@@ -2196,40 +2142,46 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>65.29090663785861</v>
+        <v>64.81388676836445</v>
       </c>
       <c r="G38" t="n">
-        <v>46.40193451244713</v>
+        <v>45.90352140211918</v>
       </c>
       <c r="H38" t="n">
-        <v>74.54474911204095</v>
+        <v>73.76372088781791</v>
       </c>
       <c r="I38" t="n">
-        <v>61.1025423081744</v>
+        <v>57.40342289611582</v>
       </c>
       <c r="J38" t="n">
-        <v>49.94101111528981</v>
+        <v>49.17468600091328</v>
       </c>
       <c r="K38" t="n">
-        <v>66.11715206192463</v>
+        <v>64.24058807851769</v>
       </c>
       <c r="L38" t="n">
-        <v>39.04387143457398</v>
+        <v>38.80808386136845</v>
       </c>
       <c r="M38" t="n">
-        <v>42.0454456421387</v>
+        <v>45.74345960544963</v>
       </c>
       <c r="N38" t="n">
-        <v>40.46088617740588</v>
+        <v>39.7963430604313</v>
       </c>
       <c r="O38" t="n">
-        <v>79.52848712428543</v>
+        <v>109.51</v>
       </c>
       <c r="P38" t="n">
-        <v>104.7954955770197</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>62.02886281072998</v>
+        <v>94.03</v>
+      </c>
+      <c r="R38" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="S38" t="n">
+        <v>79.39036375925379</v>
       </c>
     </row>
     <row r="39">
@@ -2241,40 +2193,46 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>76.13913624153663</v>
+        <v>75.49304904425108</v>
       </c>
       <c r="G39" t="n">
-        <v>50.96648745967806</v>
+        <v>52.82430017480628</v>
       </c>
       <c r="H39" t="n">
-        <v>91.80996216819196</v>
+        <v>91.12239895842757</v>
       </c>
       <c r="I39" t="n">
-        <v>68.76347403800041</v>
+        <v>65.2854929575899</v>
       </c>
       <c r="J39" t="n">
-        <v>56.53133059268873</v>
+        <v>52.18897334689802</v>
       </c>
       <c r="K39" t="n">
-        <v>81.61380024703692</v>
+        <v>83.18912601891806</v>
       </c>
       <c r="L39" t="n">
-        <v>48.81101428214004</v>
+        <v>47.58622590601446</v>
       </c>
       <c r="M39" t="n">
-        <v>45.63238836976391</v>
+        <v>40.42608515641455</v>
       </c>
       <c r="N39" t="n">
-        <v>52.55576955123058</v>
+        <v>53.00998461571746</v>
       </c>
       <c r="O39" t="n">
-        <v>81.82860194330105</v>
+        <v>101.56</v>
       </c>
       <c r="P39" t="n">
-        <v>106.8181238775737</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>58.18997177994137</v>
+        <v>89.90000000000001</v>
+      </c>
+      <c r="R39" t="n">
+        <v>93.54000000000001</v>
+      </c>
+      <c r="S39" t="n">
+        <v>77.80523496822813</v>
       </c>
     </row>
     <row r="40">
@@ -2286,40 +2244,46 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
-        <v>102.5857526555308</v>
+        <v>100.7097796152089</v>
       </c>
       <c r="G40" t="n">
-        <v>70.78974321975168</v>
+        <v>71.67818332708015</v>
       </c>
       <c r="H40" t="n">
-        <v>124.2309000465643</v>
+        <v>121.1280003996396</v>
       </c>
       <c r="I40" t="n">
-        <v>82.91312155311981</v>
+        <v>81.78771259750729</v>
       </c>
       <c r="J40" t="n">
-        <v>67.12102361042838</v>
+        <v>68.44364946303884</v>
       </c>
       <c r="K40" t="n">
-        <v>102.0244014103569</v>
+        <v>99.01180221027207</v>
       </c>
       <c r="L40" t="n">
-        <v>68.52677582364207</v>
+        <v>68.62476747432757</v>
       </c>
       <c r="M40" t="n">
-        <v>62.81529304056757</v>
+        <v>65.62049786752773</v>
       </c>
       <c r="N40" t="n">
-        <v>71.63267514331424</v>
+        <v>68.24121551238657</v>
       </c>
       <c r="O40" t="n">
-        <v>79.57499706925394</v>
+        <v>100.6</v>
       </c>
       <c r="P40" t="n">
-        <v>111.0644013725935</v>
+        <v>92.53</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.13909049069636</v>
+        <v>92.73999999999999</v>
+      </c>
+      <c r="R40" t="n">
+        <v>94.64</v>
+      </c>
+      <c r="S40" t="n">
+        <v>78.13275944777688</v>
       </c>
     </row>
     <row r="41">
@@ -2331,40 +2295,46 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>100.1222737632335</v>
+        <v>100.1730476917634</v>
       </c>
       <c r="G41" t="n">
-        <v>74.96188210338218</v>
+        <v>73.46318684229634</v>
       </c>
       <c r="H41" t="n">
-        <v>107.3705655285052</v>
+        <v>113.5361161959153</v>
       </c>
       <c r="I41" t="n">
-        <v>92.29299653005748</v>
+        <v>90.26068438260442</v>
       </c>
       <c r="J41" t="n">
-        <v>78.33853007450475</v>
+        <v>79.241063134437</v>
       </c>
       <c r="K41" t="n">
-        <v>100.61841412551</v>
+        <v>100.6427752126953</v>
       </c>
       <c r="L41" t="n">
-        <v>59.15947429151272</v>
+        <v>60.21278910465519</v>
       </c>
       <c r="M41" t="n">
-        <v>57.91603431106598</v>
+        <v>60.73186824509876</v>
       </c>
       <c r="N41" t="n">
-        <v>64.41918029326804</v>
+        <v>63.55431757919315</v>
       </c>
       <c r="O41" t="n">
-        <v>78.74258432286192</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="P41" t="n">
-        <v>112.0522151683069</v>
+        <v>100.13</v>
       </c>
       <c r="Q41" t="n">
-        <v>54.28135477007937</v>
+        <v>92.19</v>
+      </c>
+      <c r="R41" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="S41" t="n">
+        <v>78.1805202744923</v>
       </c>
     </row>
     <row r="42">
@@ -2376,40 +2346,46 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>94.24841790482029</v>
+        <v>96.62871881863322</v>
       </c>
       <c r="G42" t="n">
-        <v>68.56547583687176</v>
+        <v>68.40317791117432</v>
       </c>
       <c r="H42" t="n">
-        <v>100.6981375185932</v>
+        <v>102.1181657858875</v>
       </c>
       <c r="I42" t="n">
-        <v>86.71814607237719</v>
+        <v>85.19798519865289</v>
       </c>
       <c r="J42" t="n">
-        <v>78.20572681884285</v>
+        <v>75.21945972470915</v>
       </c>
       <c r="K42" t="n">
-        <v>95.67978305794092</v>
+        <v>93.97867548887524</v>
       </c>
       <c r="L42" t="n">
-        <v>62.01665417462756</v>
+        <v>58.34050681804396</v>
       </c>
       <c r="M42" t="n">
-        <v>59.41313460339551</v>
+        <v>60.6798865901629</v>
       </c>
       <c r="N42" t="n">
-        <v>60.50580062864579</v>
+        <v>61.70775288563971</v>
       </c>
       <c r="O42" t="n">
-        <v>77.49047880289584</v>
+        <v>107.52</v>
       </c>
       <c r="P42" t="n">
-        <v>117.4074298008712</v>
+        <v>99.53</v>
       </c>
       <c r="Q42" t="n">
-        <v>55.88905409571763</v>
+        <v>112.01</v>
+      </c>
+      <c r="R42" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="S42" t="n">
+        <v>78.49955715903263</v>
       </c>
     </row>
     <row r="43">
@@ -2421,40 +2397,46 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>84.39242329066974</v>
+        <v>82.90378747547058</v>
       </c>
       <c r="G43" t="n">
-        <v>67.29152456752985</v>
+        <v>69.31870835005928</v>
       </c>
       <c r="H43" t="n">
-        <v>86.90485034751981</v>
+        <v>87.70511652913478</v>
       </c>
       <c r="I43" t="n">
-        <v>76.49863899207175</v>
+        <v>76.70286459924331</v>
       </c>
       <c r="J43" t="n">
-        <v>70.90693753411925</v>
+        <v>73.35739669661754</v>
       </c>
       <c r="K43" t="n">
-        <v>81.76690937681101</v>
+        <v>85.28086737384125</v>
       </c>
       <c r="L43" t="n">
-        <v>47.75988736338486</v>
+        <v>48.63717110508188</v>
       </c>
       <c r="M43" t="n">
-        <v>64.34619579642563</v>
+        <v>61.45324731459228</v>
       </c>
       <c r="N43" t="n">
-        <v>37.57346745270055</v>
+        <v>41.99464612208472</v>
       </c>
       <c r="O43" t="n">
-        <v>80.22102412834525</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>118.396695377024</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>51.68634101486317</v>
+        <v>98.13</v>
+      </c>
+      <c r="R43" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="S43" t="n">
+        <v>78.01354218850042</v>
       </c>
     </row>
     <row r="44">
@@ -2466,40 +2448,46 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>83.31291136746073</v>
+        <v>85.92779270304837</v>
       </c>
       <c r="G44" t="n">
-        <v>70.04836947846103</v>
+        <v>68.34734160082893</v>
       </c>
       <c r="H44" t="n">
-        <v>88.79236463278249</v>
+        <v>89.01193749561502</v>
       </c>
       <c r="I44" t="n">
-        <v>77.80461702851051</v>
+        <v>74.96513330846466</v>
       </c>
       <c r="J44" t="n">
-        <v>75.3714695213578</v>
+        <v>73.56580996035758</v>
       </c>
       <c r="K44" t="n">
-        <v>74.66637363226724</v>
+        <v>74.91038556820601</v>
       </c>
       <c r="L44" t="n">
-        <v>44.83417946458639</v>
+        <v>44.99529403449868</v>
       </c>
       <c r="M44" t="n">
-        <v>45.43564754251354</v>
+        <v>45.1774602270304</v>
       </c>
       <c r="N44" t="n">
-        <v>45.80411093991328</v>
+        <v>49.7966240609672</v>
       </c>
       <c r="O44" t="n">
-        <v>79.79210819529283</v>
+        <v>101.02</v>
       </c>
       <c r="P44" t="n">
-        <v>118.4848452094604</v>
+        <v>95.58</v>
       </c>
       <c r="Q44" t="n">
-        <v>55.43942348487529</v>
+        <v>104.43</v>
+      </c>
+      <c r="R44" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="S44" t="n">
+        <v>77.93278752387039</v>
       </c>
     </row>
     <row r="45">
@@ -2511,37 +2499,47 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>89.03144452523573</v>
+        <v>89.53692250129254</v>
       </c>
       <c r="G45" t="n">
-        <v>66.22809221645015</v>
+        <v>63.99709166364488</v>
       </c>
       <c r="H45" t="n">
-        <v>104.6490096729139</v>
+        <v>99.53630882834159</v>
       </c>
       <c r="I45" t="n">
-        <v>80.14527377607524</v>
+        <v>83.02303959107194</v>
       </c>
       <c r="J45" t="n">
-        <v>69.54920956329822</v>
+        <v>70.14693856092822</v>
       </c>
       <c r="K45" t="n">
-        <v>91.0063189443101</v>
+        <v>92.94741347674943</v>
       </c>
       <c r="L45" t="n">
-        <v>55.0291028721935</v>
+        <v>53.7356831638103</v>
       </c>
       <c r="M45" t="n">
-        <v>48.26907957907935</v>
+        <v>46.10223033884609</v>
       </c>
       <c r="N45" t="n">
-        <v>56.84477350500982</v>
+        <v>62.83314045231837</v>
       </c>
       <c r="O45" t="n">
-        <v>79.42824772235376</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+        <v>106.54</v>
+      </c>
+      <c r="P45" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>104</v>
+      </c>
+      <c r="R45" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="S45" t="n">
+        <v>78.38237025673014</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2552,37 +2550,47 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>54.93751082330705</v>
+        <v>57.06200480111663</v>
       </c>
       <c r="G46" t="n">
-        <v>46.41261760955</v>
+        <v>44.94375640189976</v>
       </c>
       <c r="H46" t="n">
-        <v>63.02927047621412</v>
+        <v>66.63129492244329</v>
       </c>
       <c r="I46" t="n">
-        <v>46.89407259405079</v>
+        <v>49.19255662261184</v>
       </c>
       <c r="J46" t="n">
-        <v>38.50499799440635</v>
+        <v>42.3986016526295</v>
       </c>
       <c r="K46" t="n">
-        <v>55.93960185014476</v>
+        <v>54.46152894400798</v>
       </c>
       <c r="L46" t="n">
-        <v>33.62945426586426</v>
+        <v>31.71767588397162</v>
       </c>
       <c r="M46" t="n">
-        <v>38.97384458621271</v>
+        <v>36.14236765802261</v>
       </c>
       <c r="N46" t="n">
-        <v>33.24253105410176</v>
+        <v>33.12451225562469</v>
       </c>
       <c r="O46" t="n">
-        <v>77.4664001138219</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+        <v>109.04</v>
+      </c>
+      <c r="P46" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>107</v>
+      </c>
+      <c r="R46" t="n">
+        <v>105.66</v>
+      </c>
+      <c r="S46" t="n">
+        <v>78.53968328321828</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
